--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.94938385720052</v>
+        <v>3.241774876795085</v>
       </c>
       <c r="D2" t="n">
-        <v>18.5799360364406</v>
+        <v>3.019239605921598</v>
       </c>
       <c r="E2" t="n">
-        <v>12.88232954390508</v>
+        <v>2.093378550884576</v>
       </c>
       <c r="F2" t="n">
-        <v>10.84516396867105</v>
+        <v>1.762339144909046</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.321559430309433</v>
+        <v>1.027253407425283</v>
       </c>
       <c r="D3" t="n">
-        <v>4.975228116835387</v>
+        <v>0.8084745689857504</v>
       </c>
       <c r="E3" t="n">
-        <v>12.88232954390508</v>
+        <v>2.093378550884576</v>
       </c>
       <c r="F3" t="n">
-        <v>10.84516396867105</v>
+        <v>1.762339144909046</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.65638358917636</v>
+        <v>5.144162333241158</v>
       </c>
       <c r="D4" t="n">
-        <v>34.99798849239024</v>
+        <v>5.687173130013415</v>
       </c>
       <c r="E4" t="n">
-        <v>12.88232954390508</v>
+        <v>2.093378550884576</v>
       </c>
       <c r="F4" t="n">
-        <v>10.84516396867105</v>
+        <v>1.762339144909046</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.88135241460279</v>
+        <v>6.480719767372953</v>
       </c>
       <c r="D5" t="n">
-        <v>30.54208042738081</v>
+        <v>4.963088069449381</v>
       </c>
       <c r="E5" t="n">
-        <v>12.88232954390508</v>
+        <v>2.093378550884576</v>
       </c>
       <c r="F5" t="n">
-        <v>10.84516396867105</v>
+        <v>1.762339144909046</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.38334087328671</v>
+        <v>0.5497928919090904</v>
       </c>
       <c r="D6" t="n">
-        <v>6.047109431513072</v>
+        <v>0.9826552826208743</v>
       </c>
       <c r="E6" t="n">
-        <v>12.88232954390508</v>
+        <v>2.093378550884576</v>
       </c>
       <c r="F6" t="n">
-        <v>10.84516396867105</v>
+        <v>1.762339144909046</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.21181437356148</v>
+        <v>6.371919835703741</v>
       </c>
       <c r="D7" t="n">
-        <v>37.8759343119084</v>
+        <v>6.154839325685114</v>
       </c>
       <c r="E7" t="n">
-        <v>12.88232954390508</v>
+        <v>2.093378550884576</v>
       </c>
       <c r="F7" t="n">
-        <v>10.84516396867105</v>
+        <v>1.762339144909046</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.63537159565386</v>
+        <v>4.328247884293753</v>
       </c>
       <c r="D8" t="n">
-        <v>26.47862875099461</v>
+        <v>4.302777172036625</v>
       </c>
       <c r="E8" t="n">
-        <v>12.88232954390508</v>
+        <v>2.093378550884576</v>
       </c>
       <c r="F8" t="n">
-        <v>10.84516396867105</v>
+        <v>1.762339144909046</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.27274420476502</v>
+        <v>3.294320933274316</v>
       </c>
       <c r="D9" t="n">
-        <v>14.36764805746853</v>
+        <v>2.334742809338636</v>
       </c>
       <c r="E9" t="n">
-        <v>12.88232954390508</v>
+        <v>2.093378550884576</v>
       </c>
       <c r="F9" t="n">
-        <v>10.84516396867105</v>
+        <v>1.762339144909046</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.02082429892863</v>
+        <v>3.903383948575902</v>
       </c>
       <c r="D10" t="n">
-        <v>27.21836872664973</v>
+        <v>4.422984918080581</v>
       </c>
       <c r="E10" t="n">
-        <v>12.88232954390508</v>
+        <v>2.093378550884576</v>
       </c>
       <c r="F10" t="n">
-        <v>10.84516396867105</v>
+        <v>1.762339144909046</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>3.905124837953327</v>
+        <v>0.6345827861674157</v>
       </c>
       <c r="D11" t="n">
-        <v>17.4328025363091</v>
+        <v>2.832830412150229</v>
       </c>
       <c r="E11" t="n">
-        <v>12.88232954390508</v>
+        <v>2.093378550884576</v>
       </c>
       <c r="F11" t="n">
-        <v>10.84516396867105</v>
+        <v>1.762339144909046</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
